--- a/docs/xlsx/jobs-2026-10-22.xlsx
+++ b/docs/xlsx/jobs-2026-10-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="512">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,45 @@
     <t>https://www.conservationjobboard.com/job-listing-assistant-hatchery-manager---tutka-bay-lagoon-hatchery-homer-alaska/6831167426</t>
   </si>
   <si>
+    <t>Biological Science Technician (Plants) GS6/7</t>
+  </si>
+  <si>
+    <t>National Park Service</t>
+  </si>
+  <si>
+    <t>Multiple, CO</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$21.76 - $31.43 per hour</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biological-science-technician-plants-gs67-multiple-colorado/1254548180</t>
+  </si>
+  <si>
+    <t>Botany Project Manager</t>
+  </si>
+  <si>
+    <t>San Diego State University Research Foundation Soil Ecology and Restoration Group (SERG)</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$27.73 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botany-project-manager-san-diego-california/1253713083</t>
+  </si>
+  <si>
     <t>Colorado Grazing Specialist</t>
   </si>
   <si>
@@ -79,6 +118,120 @@
     <t>https://www.conservationjobboard.com/job-listing-colorado-grazing-specialist-fort-collins-colorado/5522695359</t>
   </si>
   <si>
+    <t>Deputy Director of CEQA, Licensing, and Enforcement</t>
+  </si>
+  <si>
+    <t>California Energy Commission</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$10,349 - $17,769 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-of-ceqa-licensing-and-enforcement-sacramento-ca-usa-california/8208404665</t>
+  </si>
+  <si>
+    <t>Director of Fisheries</t>
+  </si>
+  <si>
+    <t>Northwest Indian Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>Starting annual salary is $148,690 - 176,206 DOQ</t>
+  </si>
+  <si>
+    <t>admin-leadership-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-fisheries-olympia-washington/4281201087</t>
+  </si>
+  <si>
+    <t>Environmental Specialist - Shoreline/Aquatic Invasive Species</t>
+  </si>
+  <si>
+    <t>Kandiyohi County</t>
+  </si>
+  <si>
+    <t>Willmar, MN</t>
+  </si>
+  <si>
+    <t>$74,430 - $104,118 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-specialist---shorelineaquatic-invasive-species-willmar-minnesota/8687481028</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Laguna Canyon Foundation</t>
+  </si>
+  <si>
+    <t>Laguna Beach, CA</t>
+  </si>
+  <si>
+    <t>$140,000 - $160,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-laguna-beach-california/3599704726</t>
+  </si>
+  <si>
+    <t>Field Staff/Program Leader</t>
+  </si>
+  <si>
+    <t>Deer Hill Expeditions</t>
+  </si>
+  <si>
+    <t>Mancos, CO</t>
+  </si>
+  <si>
+    <t>$115 - $200 per day</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-educator-mancos-colorado/6751740526</t>
+  </si>
+  <si>
+    <t>Field Team Leader</t>
+  </si>
+  <si>
+    <t>Maine Conservation Corps</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$580 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-team-leader-augusta-maine/6754570779</t>
+  </si>
+  <si>
     <t>Fire Adapted Communities (FAC) Program Coordinator</t>
   </si>
   <si>
@@ -97,6 +250,75 @@
     <t>https://www.conservationjobboard.com/job-listing-fire-adapted-communities-fac-program-coordinator-santa-fe-new-mexico/6152817136</t>
   </si>
   <si>
+    <t>Fishery Biologist 2- Food Web Ecology</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>$69,373 - $109,122 per year</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologist-2--food-web-ecology-seattle-washington/9485841642</t>
+  </si>
+  <si>
+    <t>Forester</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Underwood, WA</t>
+  </si>
+  <si>
+    <t>$50,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forester-underwood-washington/4153061803</t>
+  </si>
+  <si>
+    <t>Microbiology Technician 2 - Fur Seal Genetics</t>
+  </si>
+  <si>
+    <t>Juneau, AK</t>
+  </si>
+  <si>
+    <t>$24.68 - $35.66 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-microbiology-technician-2---fur-seal-genetics-juneau-alaska/7691098195</t>
+  </si>
+  <si>
+    <t>Monitoring and Streamflow Manager</t>
+  </si>
+  <si>
+    <t>Clark Fork Coalition</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-monitoring-and-streamflow-manager-missoula-montana/6822554890</t>
+  </si>
+  <si>
     <t>Naturalist - Seasonal</t>
   </si>
   <si>
@@ -106,9 +328,6 @@
     <t>Girdwood, AK</t>
   </si>
   <si>
-    <t>Temporary</t>
-  </si>
-  <si>
     <t>$16 - $18 per hour</t>
   </si>
   <si>
@@ -118,6 +337,54 @@
     <t>https://www.conservationjobboard.com/job-listing-naturalist---seasonal-girdwood-alaska/3747575523</t>
   </si>
   <si>
+    <t>Naturalist Internship</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$15 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-naturalist-internship-girdwood-alaska/5796227791</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>Wildlife Restoration Foundation</t>
+  </si>
+  <si>
+    <t>Mclean, Remote</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Volunteer with possible small stipend awards</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-assistant-mclean-remote/8494402235</t>
+  </si>
+  <si>
+    <t>Orangutan and Chimpanzee Caregiver</t>
+  </si>
+  <si>
+    <t>Center for Great Apes</t>
+  </si>
+  <si>
+    <t>Wauchula, FL</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-orangutan-and-chimpanzee-caregiver-wauchula-florida/7617063693</t>
+  </si>
+  <si>
     <t>Outdoor Education Program Director</t>
   </si>
   <si>
@@ -148,10 +415,1141 @@
     <t>$29.57 per hour</t>
   </si>
   <si>
-    <t>admin-leadership</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-project-archivist-nps-yellowstone-national-park-gardiner-montana/4345930269</t>
+  </si>
+  <si>
+    <t>Project Assistant - North American Summit on Collaborating with Wildlife</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-assistant---north-american-summit-on-collaborating-with-wildlife-mclean-remote/6735468552</t>
+  </si>
+  <si>
+    <t>Purchaser IV - V (Wildlife Division Purchaser)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife Department</t>
+  </si>
+  <si>
+    <t>TBD Statewide, TX</t>
+  </si>
+  <si>
+    <t>$5,756 - $6,571 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-purchaser-iv---v-wildlife-division-purchaser-tbd-statewide-texas/6475959019</t>
+  </si>
+  <si>
+    <t>SCI Seasonal Invasive Technician</t>
+  </si>
+  <si>
+    <t>$24.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sci-seasonal-invasive-technician-san-diego-california/3439464800</t>
+  </si>
+  <si>
+    <t>SCI Seasonal Restoration Technician</t>
+  </si>
+  <si>
+    <t>$23.31 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sci-seasonal-restoration-technician-san-diego-california/8005473945</t>
+  </si>
+  <si>
+    <t>Seasonal Outdoor Educator</t>
+  </si>
+  <si>
+    <t>Upham Woods</t>
+  </si>
+  <si>
+    <t>Wisconsin Dells, WI</t>
+  </si>
+  <si>
+    <t>$17.40 - $19.70 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-outdoor-educator-wisconsin-dells-wisconsin/1256847858</t>
+  </si>
+  <si>
+    <t>Trails Program Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Central Oregon Trail Alliance</t>
+  </si>
+  <si>
+    <t>Bend, OR</t>
+  </si>
+  <si>
+    <t>$52,000 - $57,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trails-program-volunteer-coordinator-bend-oregon/3596234621</t>
+  </si>
+  <si>
+    <t>Trip Leader</t>
+  </si>
+  <si>
+    <t>Camp Pinnacle</t>
+  </si>
+  <si>
+    <t>Hendersonville, NC</t>
+  </si>
+  <si>
+    <t>$350 - $450 per week</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trip-leader-hendersonville-north-carolina/8624667387</t>
+  </si>
+  <si>
+    <t>Wetland Permitting Specialist - Environmental Planner 3 - Permanent - 2026-08839</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>$5,779 - $7,774 per month</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-permitting-specialist---environmental-planner-3---permanent---2026-08839-olympia-washington/5688507472</t>
+  </si>
+  <si>
+    <t>Whale Watching Captain</t>
+  </si>
+  <si>
+    <t>San Juan Safaris</t>
+  </si>
+  <si>
+    <t>Friday Harbor, WA</t>
+  </si>
+  <si>
+    <t>$35 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology-outdoor-recreation-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-whale-watching-captain-friday-harbor-washington/4880987425</t>
+  </si>
+  <si>
+    <t>Wildlife Photography &amp; Film Specialist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-photography--film-specialist-mclean-remote/2544262985</t>
+  </si>
+  <si>
+    <t>Senior Software Product Manager</t>
+  </si>
+  <si>
+    <t>Wentworth Executive Recruiting | Retained Search</t>
+  </si>
+  <si>
+    <t>California, United States, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-software-product-manager/</t>
+  </si>
+  <si>
+    <t>Accounting Coordinator</t>
+  </si>
+  <si>
+    <t>U.S. Grains &amp; BioProducts Council</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0647580d3514090906ebd633ac2de73-accounting-coordinator-us-grains-bioproducts-council-washington</t>
+  </si>
+  <si>
+    <t>Administrative Assistant I (Greenpoint YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c64fe9b691904ffc960d43ff76287883-administrative-assistant-i-greenpoint-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Advancement Director, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee1c2e291f32465392ae1e44e4489a68-advancement-director-mid-atlantic-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Advisor, Public Health Data Analytics &amp; Visualization</t>
+  </si>
+  <si>
+    <t>BME Strategies</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 87360.00 - 120640.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/ca37cb6e83eb4378b608e444db35fad6-advisor-public-health-data-analytics-visualization-bme-strategies-north-andover</t>
+  </si>
+  <si>
+    <t>Assistant Director of Development-The Friedman Brain Institute (Office of Development)</t>
+  </si>
+  <si>
+    <t>Mount Sinai Health System, New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 65885.00 - 98827.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64e4ad83486f4c37b11997e96111220d-assistant-director-of-development-the-friedman-brain-institute-office-of-development-mount-sinai-health-system-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Attorney- Montana Health Justice Partnership</t>
+  </si>
+  <si>
+    <t>Montana Legal Services Association</t>
+  </si>
+  <si>
+    <t>Helena, Montana</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28f2f8b753f44190ac39796b1b7b87ef-attorney-montana-health-justice-partnership-montana-legal-services-association-helena</t>
+  </si>
+  <si>
+    <t>Bike Tour Coordinator</t>
+  </si>
+  <si>
+    <t>Parks &amp; Trails New York</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b187fcb75d9d4b03a1d7841a90b9741f-bike-tour-coordinator-parks-trails-new-york-albany</t>
+  </si>
+  <si>
+    <t>Care Manager</t>
+  </si>
+  <si>
+    <t>Osborne Association Inc</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0048c9f3f01b40f98199391ea9f133ca-care-manager-osborne-association-inc-bronx</t>
+  </si>
+  <si>
+    <t>Chapter Organizer (Independent Contractor)</t>
+  </si>
+  <si>
+    <t>National Parents Organization</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Family, Men</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1eba5d5096b4670bc89fe944be98166-chapter-organizer-independent-contractor-national-parents-organization-haverhill</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer (COO)</t>
+  </si>
+  <si>
+    <t>I'm Your Neighbor Books</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45a6c6a232dd4e91b94df3f2b0727eb1-chief-operating-officer-coo-im-your-neighbor-books-portland</t>
+  </si>
+  <si>
+    <t>Choir Executive Director</t>
+  </si>
+  <si>
+    <t>Schola Cantorum</t>
+  </si>
+  <si>
+    <t>Los Altos, California</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05a11ece7969418caf653eb22e24c484-choir-executive-director-schola-cantorum-los-altos</t>
+  </si>
+  <si>
+    <t>Client Services Coordinator, Non-Profit in Richmond, VA</t>
+  </si>
+  <si>
+    <t>Warren Whitney Management Consulting</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd7f0d6b88944f3ebe92b02d60b8d858-client-services-coordinator-non-profit-in-richmond-va-warren-whitney-management-consulting-richmond</t>
+  </si>
+  <si>
+    <t>Communication and Marketing Associate</t>
+  </si>
+  <si>
+    <t>Margaret Fuller Neighborhood House</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbeafd5a19a9441a9383d150a5c073bb-communication-and-marketing-associate-margaret-fuller-neighborhood-house-cambridge</t>
+  </si>
+  <si>
+    <t>Communications Director</t>
+  </si>
+  <si>
+    <t>Connecticut AFL-CIO</t>
+  </si>
+  <si>
+    <t>Rocky Hill, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/941514bb36c1497fa44f6c9c2a12a813-communications-director-connecticut-afl-cio-rocky-hill</t>
+  </si>
+  <si>
+    <t>New Jersey Future</t>
+  </si>
+  <si>
+    <t>Trenton, NJ</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c96be6d371d94109acd0b894e246abac-communications-director-new-jersey-future-trenton</t>
+  </si>
+  <si>
+    <t>Community Enrollment Rep. (Sustainability + Nutrition) - Tacoma</t>
+  </si>
+  <si>
+    <t>Full Circle</t>
+  </si>
+  <si>
+    <t>Tacoma, Washington</t>
+  </si>
+  <si>
+    <t>USD 34650.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/75db3b65b8844e8bb28926cc67e2a24e-community-enrollment-rep-sustainability-nutrition-tacoma-full-circle-tacoma</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Pilsen Neighbors Community Council</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 38000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7adaf7635d4b4c03a06347307891bed1-community-organizer-pilsen-neighbors-community-council-chicago</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Plan International USA</t>
+  </si>
+  <si>
+    <t>Warwick, RI</t>
+  </si>
+  <si>
+    <t>USD 101291.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42725655951340d6a0ee0cf6ab7bdbdd-controller-plan-international-usa-warwick</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d4e4ccb5d7a427f9418e6047db793a3-controller-plan-international-usa-warwick</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>ALL STARS PROJECT INC.</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e5ebb42b0bfc4185a5c7208cb8ceee9a-development-manager-all-stars-project-inc-newark</t>
+  </si>
+  <si>
+    <t>Director of Development Operations (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>Accelerate Change</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5ddfa78228442c68b2bc0665efcd889-director-of-development-operations-full-time-remote-accelerate-change-boston</t>
+  </si>
+  <si>
+    <t>Director of Legal Services</t>
+  </si>
+  <si>
+    <t>Shalom Task Force, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/749d5798bb0e420881944e092bba6aa9-director-of-legal-services-shalom-task-force-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director of People Operations (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f4843bb71b84062b3652679ec4dea7d-director-of-people-operations-full-time-remote-accelerate-change-boston</t>
+  </si>
+  <si>
+    <t>Director of Policy and Advocacy</t>
+  </si>
+  <si>
+    <t>National Youth Employment Coalition</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b64e5d4e16c4bddb7abd0bb564501fa-director-of-policy-and-advocacy-national-youth-employment-coalition-washington</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>The Summer Learning Collaborative, Inc.</t>
+  </si>
+  <si>
+    <t>New Castle, Delaware</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf905242863d4624bcdc311c5bde32d0-director-of-programs-the-summer-learning-collaborative-inc-new-castle</t>
+  </si>
+  <si>
+    <t>Drupal Developer, Ongoing Site Maintenance (Contract, Remote)</t>
+  </si>
+  <si>
+    <t>ITP International</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53447a0159f14b7d841f4a6c35172244-drupal-developer-ongoing-site-maintenance-contract-remote-itp-international-corte-madera</t>
+  </si>
+  <si>
+    <t>Education Advocate, Immigrant Students' Rights Project</t>
+  </si>
+  <si>
+    <t>Advocates for Children of New York, Inc.</t>
+  </si>
+  <si>
+    <t>USD 62489.00 - 68003.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12687369f84a4cb7b55de7793a580135-education-advocate-immigrant-students-rights-project-advocates-for-children-of-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Laguna Beach, California</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Volunteering</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64a71ecaeba34ffdaa4285a83ee86131-executive-director-laguna-canyon-foundation-laguna-beach</t>
+  </si>
+  <si>
+    <t>Executive Director - Waterford Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Waterford Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Waterford, Virginia</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22709fe647fc4974b1076917e12ee5b5-executive-director-waterford-foundation-inc-waterford-foundation-inc-waterford</t>
+  </si>
+  <si>
+    <t>Executive Director for the Master of Professional Accountancy Program</t>
+  </si>
+  <si>
+    <t>University of California San Diego</t>
+  </si>
+  <si>
+    <t>La Jolla, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c0bb3c557695437aa1d2edc60f9250ab-executive-director-for-the-master-of-professional-accountancy-program-university-of-california-san-diego-la-jolla</t>
+  </si>
+  <si>
+    <t>Executive Director, Midwest Chapter</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a900ecbc293e4863b0e462d7e6bf4ca3-executive-director-midwest-chapter-parkinsons-foundation-chicago</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>Triangle Land Conservancy</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4914c46e02f14526902d7c73d9e995e6-facilities-manager-triangle-land-conservancy-raleigh</t>
+  </si>
+  <si>
+    <t>Grants and Partnerships Manager</t>
+  </si>
+  <si>
+    <t>SIFF (Seattle International Film Festival)</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 68500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d2bfbac38ad44fc97977e40e3d5a536-grants-and-partnerships-manager-siff-seattle-international-film-festival-seattle</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>National Association of Criminal Defense Lawyers</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a5fa78aeed045a2a7f861156e085dce-grants-manager-national-association-of-criminal-defense-lawyers-washington</t>
+  </si>
+  <si>
+    <t>Home Delivered Meals Driver - Full-time</t>
+  </si>
+  <si>
+    <t>AgeSpan</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 18.06 - 18.06/hour</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Disability, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31668d53bac940bbac56b4a0ad7c31ad-home-delivered-meals-driver-full-time-agespan-lowell</t>
+  </si>
+  <si>
+    <t>Human Resources &amp; Office Coordinator</t>
+  </si>
+  <si>
+    <t>PaintCare &amp; American Coatings Association</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/360dcc5cd97c456e8dbccd41f0a772c5-human-resources-office-coordinator-paintcare-american-coatings-association-washington</t>
+  </si>
+  <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ae110ad874d46199a81009ee5c29105-human-resources-generalist-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Immigration Attorney - PT</t>
+  </si>
+  <si>
+    <t>AIDS Center of Queens County, Inc. - ACQC</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 51.00 - 51.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38f7124ff1e9410f8ee37cfff3b3da27-immigration-attorney-pt-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
+    <t>International Director 2027</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00 - 200.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/937eec90609b452d92e1f7964df8ca4c-international-director-2027-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Janitorial Supervisor</t>
+  </si>
+  <si>
+    <t>Toolworks</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 22.31 - 22.31/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63e7a81cb3cf477ebf57a8544f6a3afb-janitorial-supervisor-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Junior Research Analyst: Data Management</t>
+  </si>
+  <si>
+    <t>The Policy and Research Group</t>
+  </si>
+  <si>
+    <t>New Orleans, LA</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1afeb73d057541138a287dedffa6f866-junior-research-analyst-data-management-the-policy-and-research-group-new-orleans</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Leadership Greater Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4724cd509ebf4ac7a669969f181f7c7d-marketing-communications-manager-leadership-greater-washington-washington</t>
+  </si>
+  <si>
+    <t>Marketing and Content Manager</t>
+  </si>
+  <si>
+    <t>Brooklyn Arts Council, Inc.</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b05afb9092e44e0dab7b90b37706d65c-marketing-and-content-manager-brooklyn-arts-council-inc-new-york</t>
+  </si>
+  <si>
+    <t>Mass-Care Organizer</t>
+  </si>
+  <si>
+    <t>Mass-Care</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/024c500481ea44f9bd08effd56c464fe-mass-care-organizer-mass-care-boston</t>
+  </si>
+  <si>
+    <t>Metascience Fellowship</t>
+  </si>
+  <si>
+    <t>Federation of American Scientists</t>
+  </si>
+  <si>
+    <t>USD 174000.00 - 174000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f7105113a604997a4f1a825105a461a-metascience-fellowship-federation-of-american-scientists-washington</t>
+  </si>
+  <si>
+    <t>Office and Facilities Manager</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c2177f805164ed89fb39c96a48d6faf-office-and-facilities-manager-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Officer, Business Partnerships</t>
+  </si>
+  <si>
+    <t>City Harvest</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23cee5036ae7426fa5212af0a3fb8f2f-officer-business-partnerships-city-harvest-kings-county</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Spark Climate Solutions</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65b2c8be4d4c4424b98c7c54d30adffd-operations-coordinator-spark-climate-solutions-san-francisco</t>
+  </si>
+  <si>
+    <t>Operations Specialist</t>
+  </si>
+  <si>
+    <t>Sanar Institute</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad27c925ccd8424d962e7a12641ec286-operations-specialist-sanar-institute-newark</t>
+  </si>
+  <si>
+    <t>President &amp; CEO</t>
+  </si>
+  <si>
+    <t>Adagio Health</t>
+  </si>
+  <si>
+    <t>Pittsburgh, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 250000.00 - 300000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6b83300d23c4db3a10b48c766302d0c-president-ceo-adagio-health-pittsburgh</t>
+  </si>
+  <si>
+    <t>PT Legal Navigator</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9cff741ec6344d7a259f4e5ac1671eb-pt-legal-navigator-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
+    <t>Recruiter</t>
+  </si>
+  <si>
+    <t>BESTWORK INDUSTRIES FOR THE BLIND INC</t>
+  </si>
+  <si>
+    <t>CHERRY HILL, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Economic Development, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0feb028d4ee465c9a9d2b66f74db446-recruiter-bestwork-industries-for-the-blind-inc-cherry-hill</t>
+  </si>
+  <si>
+    <t>Registered Nurse (part time hourly – PRN or 5+ hours per week)</t>
+  </si>
+  <si>
+    <t>Jewish Family Service of Metrowest</t>
+  </si>
+  <si>
+    <t>Framingham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b6c1e18a43a43fb84414448fdb6f80f-registered-nurse-part-time-hourly-prn-or-5-hours-per-week-jewish-family-service-of-metrowest-framingham</t>
+  </si>
+  <si>
+    <t>Research Manager</t>
+  </si>
+  <si>
+    <t>United Way of Northern New Jersey</t>
+  </si>
+  <si>
+    <t>Cedar Knolls, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/faa4583e8c45447c8b4f439540a4b2db-research-manager-united-way-of-northern-new-jersey-cedar-knolls</t>
+  </si>
+  <si>
+    <t>Senior Attorney- Equal Access and Housing</t>
+  </si>
+  <si>
+    <t>Disability Rights California</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 89436.00 - 130958.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/611a4727475f4619b05ff53cade42d4e-senior-attorney-equal-access-and-housing-disability-rights-california-sacramento</t>
+  </si>
+  <si>
+    <t>Senior Grant Writer</t>
+  </si>
+  <si>
+    <t>Elevate</t>
+  </si>
+  <si>
+    <t>USD 62500.00 - 62500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/22b18aa754b34708b76c7b12ac3e227e-senior-grant-writer-elevate-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager of Finance</t>
+  </si>
+  <si>
+    <t>Good360</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0098eb0b3bf42f88274c359f2cec1ff-senior-manager-of-finance-good360-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Manager, Community Relations</t>
+  </si>
+  <si>
+    <t>Spoonfuls</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 98000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97b3643dec4e4b549a6fbf3ff6151d7e-senior-manager-community-relations-spoonfuls-newton</t>
+  </si>
+  <si>
+    <t>Senior Manager, Risk Behavior Prevention (CO Only)</t>
+  </si>
+  <si>
+    <t>Action for Healthy Kids</t>
+  </si>
+  <si>
+    <t>Remote (Colorado)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d131c2b7199149a8bcd17b3c32e8fb8c-senior-manager-risk-behavior-prevention-co-only-action-for-healthy-kids-chicago</t>
+  </si>
+  <si>
+    <t>Senior Vice President, Partnership Fund for New York City</t>
+  </si>
+  <si>
+    <t>Partnership for New York City</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 230000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f549b89093564030a1ea6c34f66d644a-senior-vice-president-partnership-fund-for-new-york-city-partnership-for-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7924002f6dc34c65ad76eb8e983ab313-staff-attorney-shalom-task-force-inc-new-york</t>
+  </si>
+  <si>
+    <t>SUBDIRECTOR/A DE INSTITUTOS SUPERIORES</t>
+  </si>
+  <si>
+    <t>Cruz Roja Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>ARS 1.00 - 1.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acfd94fe106142d3b559a8b46a06594f-subdirectora-de-institutos-superiores-cruz-roja-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Volunteer &amp; Community Engagement Associate</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Volunteering, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57b772ac3c81466b8307a3817313c365-volunteer-community-engagement-associate-jewish-family-service-of-metrowest-framingham</t>
+  </si>
+  <si>
+    <t>Youth Engagement Specialist</t>
+  </si>
+  <si>
+    <t>NYC Campaign Finance Board</t>
+  </si>
+  <si>
+    <t>USD 80000.01 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c0c35d4b01e14b72860cde1654a4c164-youth-engagement-specialist-nyc-campaign-finance-board-new-york</t>
   </si>
 </sst>
 </file>
@@ -537,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -610,53 +2008,53 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -702,7 +2100,7 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
         <v>43</v>
@@ -712,6 +2110,584 @@
       </c>
       <c r="H7" s="2" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -723,6 +2699,31 @@
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -731,7 +2732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -770,8 +2771,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -779,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -818,8 +2845,1549 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" t="s">
+        <v>237</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" t="s">
+        <v>243</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" t="s">
+        <v>248</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" t="s">
+        <v>264</v>
+      </c>
+      <c r="F15" t="s">
+        <v>265</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" t="s">
+        <v>269</v>
+      </c>
+      <c r="F16" t="s">
+        <v>270</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>278</v>
+      </c>
+      <c r="B18" t="s">
+        <v>279</v>
+      </c>
+      <c r="C18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
+        <v>287</v>
+      </c>
+      <c r="F19" t="s">
+        <v>288</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>284</v>
+      </c>
+      <c r="B20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" t="s">
+        <v>287</v>
+      </c>
+      <c r="F20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" t="s">
+        <v>294</v>
+      </c>
+      <c r="F21" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>296</v>
+      </c>
+      <c r="B22" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F22" t="s">
+        <v>299</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C23" t="s">
+        <v>213</v>
+      </c>
+      <c r="D23" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" t="s">
+        <v>303</v>
+      </c>
+      <c r="F23" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>306</v>
+      </c>
+      <c r="B24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C24" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" t="s">
+        <v>298</v>
+      </c>
+      <c r="F24" t="s">
+        <v>299</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B25" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" t="s">
+        <v>310</v>
+      </c>
+      <c r="F25" t="s">
+        <v>311</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" t="s">
+        <v>314</v>
+      </c>
+      <c r="C26" t="s">
+        <v>315</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>316</v>
+      </c>
+      <c r="F26" t="s">
+        <v>317</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C27" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E27" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" t="s">
+        <v>321</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>323</v>
+      </c>
+      <c r="B28" t="s">
+        <v>324</v>
+      </c>
+      <c r="C28" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" t="s">
+        <v>326</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>328</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>329</v>
+      </c>
+      <c r="F29" t="s">
+        <v>330</v>
+      </c>
+      <c r="G29" t="s">
+        <v>331</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>333</v>
+      </c>
+      <c r="B30" t="s">
+        <v>334</v>
+      </c>
+      <c r="C30" t="s">
+        <v>335</v>
+      </c>
+      <c r="D30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" t="s">
+        <v>336</v>
+      </c>
+      <c r="F30" t="s">
+        <v>337</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s">
+        <v>340</v>
+      </c>
+      <c r="C31" t="s">
+        <v>341</v>
+      </c>
+      <c r="D31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>343</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" t="s">
+        <v>344</v>
+      </c>
+      <c r="F32" t="s">
+        <v>345</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" t="s">
+        <v>349</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
+        <v>350</v>
+      </c>
+      <c r="F33" t="s">
+        <v>351</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>353</v>
+      </c>
+      <c r="B34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D34" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" t="s">
+        <v>356</v>
+      </c>
+      <c r="F34" t="s">
+        <v>248</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>358</v>
+      </c>
+      <c r="B35" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" t="s">
+        <v>360</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" t="s">
+        <v>361</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" t="s">
+        <v>364</v>
+      </c>
+      <c r="C36" t="s">
+        <v>365</v>
+      </c>
+      <c r="D36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" t="s">
+        <v>366</v>
+      </c>
+      <c r="F36" t="s">
+        <v>367</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>369</v>
+      </c>
+      <c r="B37" t="s">
+        <v>370</v>
+      </c>
+      <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" t="s">
+        <v>371</v>
+      </c>
+      <c r="F37" t="s">
+        <v>372</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>374</v>
+      </c>
+      <c r="B38" t="s">
+        <v>375</v>
+      </c>
+      <c r="C38" t="s">
+        <v>360</v>
+      </c>
+      <c r="D38" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" t="s">
+        <v>310</v>
+      </c>
+      <c r="F38" t="s">
+        <v>376</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>378</v>
+      </c>
+      <c r="B39" t="s">
+        <v>379</v>
+      </c>
+      <c r="C39" t="s">
+        <v>380</v>
+      </c>
+      <c r="D39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" t="s">
+        <v>381</v>
+      </c>
+      <c r="F39" t="s">
+        <v>382</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>384</v>
+      </c>
+      <c r="B40" t="s">
+        <v>385</v>
+      </c>
+      <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
+        <v>236</v>
+      </c>
+      <c r="E40" t="s">
+        <v>386</v>
+      </c>
+      <c r="F40" t="s">
+        <v>387</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>389</v>
+      </c>
+      <c r="B41" t="s">
+        <v>390</v>
+      </c>
+      <c r="C41" t="s">
+        <v>391</v>
+      </c>
+      <c r="D41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" t="s">
+        <v>392</v>
+      </c>
+      <c r="F41" t="s">
+        <v>182</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>394</v>
+      </c>
+      <c r="B42" t="s">
+        <v>395</v>
+      </c>
+      <c r="C42" t="s">
+        <v>396</v>
+      </c>
+      <c r="D42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" t="s">
+        <v>397</v>
+      </c>
+      <c r="F42" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>399</v>
+      </c>
+      <c r="B43" t="s">
+        <v>400</v>
+      </c>
+      <c r="C43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>336</v>
+      </c>
+      <c r="F43" t="s">
+        <v>299</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>402</v>
+      </c>
+      <c r="B44" t="s">
+        <v>403</v>
+      </c>
+      <c r="C44" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" t="s">
+        <v>404</v>
+      </c>
+      <c r="F44" t="s">
+        <v>248</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>406</v>
+      </c>
+      <c r="B45" t="s">
+        <v>407</v>
+      </c>
+      <c r="C45" t="s">
+        <v>365</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
+        <v>408</v>
+      </c>
+      <c r="F45" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>410</v>
+      </c>
+      <c r="B46" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46" t="s">
+        <v>187</v>
+      </c>
+      <c r="D46" t="s">
+        <v>236</v>
+      </c>
+      <c r="E46" t="s">
+        <v>412</v>
+      </c>
+      <c r="F46" t="s">
+        <v>413</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47" t="s">
+        <v>360</v>
+      </c>
+      <c r="D47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" t="s">
+        <v>416</v>
+      </c>
+      <c r="F47" t="s">
+        <v>417</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>419</v>
+      </c>
+      <c r="B48" t="s">
+        <v>420</v>
+      </c>
+      <c r="C48" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" t="s">
+        <v>188</v>
+      </c>
+      <c r="E48" t="s">
+        <v>421</v>
+      </c>
+      <c r="F48" t="s">
+        <v>422</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>424</v>
+      </c>
+      <c r="B49" t="s">
+        <v>425</v>
+      </c>
+      <c r="C49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E49" t="s">
+        <v>426</v>
+      </c>
+      <c r="F49" t="s">
+        <v>427</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>429</v>
+      </c>
+      <c r="B50" t="s">
+        <v>430</v>
+      </c>
+      <c r="C50" t="s">
+        <v>293</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" t="s">
+        <v>431</v>
+      </c>
+      <c r="F50" t="s">
+        <v>432</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>434</v>
+      </c>
+      <c r="B51" t="s">
+        <v>435</v>
+      </c>
+      <c r="C51" t="s">
+        <v>436</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" t="s">
+        <v>437</v>
+      </c>
+      <c r="F51" t="s">
+        <v>438</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" t="s">
+        <v>379</v>
+      </c>
+      <c r="C52" t="s">
+        <v>380</v>
+      </c>
+      <c r="D52" t="s">
+        <v>195</v>
+      </c>
+      <c r="E52" t="s">
+        <v>441</v>
+      </c>
+      <c r="F52" t="s">
+        <v>382</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>443</v>
+      </c>
+      <c r="B53" t="s">
+        <v>444</v>
+      </c>
+      <c r="C53" t="s">
+        <v>445</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>446</v>
+      </c>
+      <c r="F53" t="s">
+        <v>447</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>449</v>
+      </c>
+      <c r="B54" t="s">
+        <v>450</v>
+      </c>
+      <c r="C54" t="s">
+        <v>451</v>
+      </c>
+      <c r="D54" t="s">
+        <v>195</v>
+      </c>
+      <c r="E54" t="s">
+        <v>452</v>
+      </c>
+      <c r="F54" t="s">
+        <v>453</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>455</v>
+      </c>
+      <c r="B55" t="s">
+        <v>456</v>
+      </c>
+      <c r="C55" t="s">
+        <v>457</v>
+      </c>
+      <c r="D55" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" t="s">
+        <v>458</v>
+      </c>
+      <c r="F55" t="s">
+        <v>459</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>461</v>
+      </c>
+      <c r="B56" t="s">
+        <v>462</v>
+      </c>
+      <c r="C56" t="s">
+        <v>463</v>
+      </c>
+      <c r="D56" t="s">
+        <v>188</v>
+      </c>
+      <c r="E56" t="s">
+        <v>464</v>
+      </c>
+      <c r="F56" t="s">
+        <v>465</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>467</v>
+      </c>
+      <c r="B57" t="s">
+        <v>468</v>
+      </c>
+      <c r="C57" t="s">
+        <v>207</v>
+      </c>
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" t="s">
+        <v>469</v>
+      </c>
+      <c r="F57" t="s">
+        <v>182</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>471</v>
+      </c>
+      <c r="B58" t="s">
+        <v>472</v>
+      </c>
+      <c r="C58" t="s">
+        <v>473</v>
+      </c>
+      <c r="D58" t="s">
+        <v>188</v>
+      </c>
+      <c r="E58" t="s">
+        <v>474</v>
+      </c>
+      <c r="F58" t="s">
+        <v>475</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>477</v>
+      </c>
+      <c r="B59" t="s">
+        <v>478</v>
+      </c>
+      <c r="C59" t="s">
+        <v>479</v>
+      </c>
+      <c r="D59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" t="s">
+        <v>480</v>
+      </c>
+      <c r="F59" t="s">
+        <v>481</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>483</v>
+      </c>
+      <c r="B60" t="s">
+        <v>484</v>
+      </c>
+      <c r="C60" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" t="s">
+        <v>486</v>
+      </c>
+      <c r="F60" t="s">
+        <v>487</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>489</v>
+      </c>
+      <c r="B61" t="s">
+        <v>490</v>
+      </c>
+      <c r="C61" t="s">
+        <v>491</v>
+      </c>
+      <c r="D61" t="s">
+        <v>188</v>
+      </c>
+      <c r="E61" t="s">
+        <v>492</v>
+      </c>
+      <c r="F61" t="s">
+        <v>493</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>495</v>
+      </c>
+      <c r="B62" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" t="s">
+        <v>213</v>
+      </c>
+      <c r="D62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" t="s">
+        <v>496</v>
+      </c>
+      <c r="F62" t="s">
+        <v>497</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>499</v>
+      </c>
+      <c r="B63" t="s">
+        <v>500</v>
+      </c>
+      <c r="C63" t="s">
+        <v>501</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63" t="s">
+        <v>502</v>
+      </c>
+      <c r="F63" t="s">
+        <v>317</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>504</v>
+      </c>
+      <c r="B64" t="s">
+        <v>450</v>
+      </c>
+      <c r="C64" t="s">
+        <v>451</v>
+      </c>
+      <c r="D64" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" t="s">
+        <v>505</v>
+      </c>
+      <c r="F64" t="s">
+        <v>506</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>508</v>
+      </c>
+      <c r="B65" t="s">
+        <v>509</v>
+      </c>
+      <c r="C65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" t="s">
+        <v>510</v>
+      </c>
+      <c r="F65" t="s">
+        <v>182</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-22.xlsx
+++ b/docs/xlsx/jobs-2026-10-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="771">
   <si>
     <t>Title</t>
   </si>
@@ -613,6 +613,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c64fe9b691904ffc960d43ff76287883-administrative-assistant-i-greenpoint-ymca-ymca-of-greater-new-york-kings-county</t>
   </si>
   <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Plant Powered Metro New York</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d666eafbb40e4781bb99a231baa69b34-administrative-coordinator-plant-powered-metro-new-york-new-york</t>
+  </si>
+  <si>
     <t>Advancement Director, Mid-Atlantic</t>
   </si>
   <si>
@@ -637,9 +655,6 @@
     <t>BME Strategies</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 87360.00 - 120640.00/year</t>
   </si>
   <si>
@@ -649,6 +664,33 @@
     <t>https://www.idealist.org/en/consultant-job/ca37cb6e83eb4378b608e444db35fad6-advisor-public-health-data-analytics-visualization-bme-strategies-north-andover</t>
   </si>
   <si>
+    <t>Anti-Hunger Program Associate</t>
+  </si>
+  <si>
+    <t>Maryland Hunger Solutions</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d8e4db3c31c485080bf4de37915a349-anti-hunger-program-associate-maryland-hunger-solutions-washington</t>
+  </si>
+  <si>
+    <t>Food Research &amp; Action Center (FRAC)</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/110809ccf3a0418fb3850659bc16692d-anti-hunger-program-associate-food-research-action-center-frac-washington</t>
+  </si>
+  <si>
     <t>Assistant Director of Development-The Friedman Brain Institute (Office of Development)</t>
   </si>
   <si>
@@ -664,6 +706,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/64e4ad83486f4c37b11997e96111220d-assistant-director-of-development-the-friedman-brain-institute-office-of-development-mount-sinai-health-system-new-york-new-york</t>
   </si>
   <si>
+    <t>Attorney (Temporary)</t>
+  </si>
+  <si>
+    <t>National Center for Youth Law (NCYL)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 107650.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35d2fbea3e9a45b88a71c45662d2a4ef-attorney-temporary-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
     <t>Attorney- Montana Health Justice Partnership</t>
   </si>
   <si>
@@ -703,6 +763,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b187fcb75d9d4b03a1d7841a90b9741f-bike-tour-coordinator-parks-trails-new-york-albany</t>
   </si>
   <si>
+    <t>C-12-26 Early Learning Specialist</t>
+  </si>
+  <si>
+    <t>GPB -Georgia Public Broadcasting</t>
+  </si>
+  <si>
+    <t>Atlanta, GA</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Media, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b5648cbf8f34b70a1edc98b54be472c-c-12-26-early-learning-specialist-gpb-georgia-public-broadcasting-atlanta</t>
+  </si>
+  <si>
     <t>Care Manager</t>
   </si>
   <si>
@@ -718,6 +796,24 @@
     <t>https://www.idealist.org/en/job/0048c9f3f01b40f98199391ea9f133ca-care-manager-osborne-association-inc-bronx</t>
   </si>
   <si>
+    <t>Case Manager / Aftercare Associate</t>
+  </si>
+  <si>
+    <t>ACE (Association of Community Employment Programs for the Homeless, Inc.)</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1732f127c614cdbbd6fa7cf23748ce6-case-manager-aftercare-associate-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
     <t>Chapter Organizer (Independent Contractor)</t>
   </si>
   <si>
@@ -766,6 +862,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/05a11ece7969418caf653eb22e24c484-choir-executive-director-schola-cantorum-los-altos</t>
   </si>
   <si>
+    <t>Clean Water Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c4904e050e54deba41b3112a90bd50e-clean-water-associate-environment-america-portland</t>
+  </si>
+  <si>
     <t>Client Services Coordinator, Non-Profit in Richmond, VA</t>
   </si>
   <si>
@@ -781,6 +895,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/fd7f0d6b88944f3ebe92b02d60b8d858-client-services-coordinator-non-profit-in-richmond-va-warren-whitney-management-consulting-richmond</t>
   </si>
   <si>
+    <t>Colorado Zero Waste Advocate</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d9823a562cf495087f7d209725cd0aa-colorado-zero-waste-advocate-us-pirg-denver</t>
+  </si>
+  <si>
     <t>Communication and Marketing Associate</t>
   </si>
   <si>
@@ -868,6 +997,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7adaf7635d4b4c03a06347307891bed1-community-organizer-pilsen-neighbors-community-council-chicago</t>
   </si>
   <si>
+    <t>Content and Editorial Lead</t>
+  </si>
+  <si>
+    <t>Portland State University Foundation</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 83000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13ca41b908f64eea903f0c39f3de1b5a-content-and-editorial-lead-portland-state-university-foundation-portland</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -889,6 +1036,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/1d4e4ccb5d7a427f9418e6047db793a3-controller-plan-international-usa-warwick</t>
   </si>
   <si>
+    <t>Controller, Accounting, &amp; Financial Operations</t>
+  </si>
+  <si>
+    <t>First Book</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98bfdc2446804fe89abbbc74dbceb6c8-controller-accounting-financial-operations-first-book-washington</t>
+  </si>
+  <si>
+    <t>Coordinator, Meridian Center for Global Leadership</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 52238.00 - 55125.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/441b189b4dfc459688d6d1e3bd30c659-coordinator-meridian-center-for-global-leadership-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity of Oregon</t>
+  </si>
+  <si>
+    <t>Tualatin, Oregon</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b6d6af84ac445819fc1de6e337cac64-data-analyst-habitat-for-humanity-of-oregon-tualatin</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -904,6 +1096,69 @@
     <t>https://www.idealist.org/en/job/e5ebb42b0bfc4185a5c7208cb8ceee9a-development-manager-all-stars-project-inc-newark</t>
   </si>
   <si>
+    <t>Rahab's Sisters</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98ecdd3ee0b04da6b4c7e9c6ba1a1dfe-development-manager-rahabs-sisters-portland</t>
+  </si>
+  <si>
+    <t>Breakthrough Greater Boston</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 79600.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ebd69446b874aec9b29ea44d8f732dc-development-manager-breakthrough-greater-boston-cambridge</t>
+  </si>
+  <si>
+    <t>Digital Campaign Manager</t>
+  </si>
+  <si>
+    <t>Vision First</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b91b55fbff4f4ee9b76080b8bc8ac029-digital-campaign-manager-vision-first-washington</t>
+  </si>
+  <si>
+    <t>Digital Operations Associate</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 68300.00 - 89200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/456af7db876345bbad7ebd36b9bb2812-digital-operations-associate-earthjustice-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Administrative Operations</t>
+  </si>
+  <si>
+    <t>USD 1280.00 - 1280.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f7bc2fb259e4e15ae090b0f789fa4c2-director-of-administrative-operations-plant-powered-metro-new-york-new-york</t>
+  </si>
+  <si>
     <t>Director of Development Operations (Full Time, Remote)</t>
   </si>
   <si>
@@ -934,6 +1189,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/749d5798bb0e420881944e092bba6aa9-director-of-legal-services-shalom-task-force-inc-new-york</t>
   </si>
   <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>High Impact Professionals</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32c252e405984d34ada094626795e84d-director-of-operations-high-impact-professionals-towson</t>
+  </si>
+  <si>
     <t>Director of People Operations (Full Time, Remote)</t>
   </si>
   <si>
@@ -967,12 +1234,24 @@
     <t>USD 60000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/cf905242863d4624bcdc311c5bde32d0-director-of-programs-the-summer-learning-collaborative-inc-new-castle</t>
   </si>
   <si>
+    <t>Director, FP&amp;A and Grant Management</t>
+  </si>
+  <si>
+    <t>Human Rights Watch</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/430c2e3960114df1a70b4716e25bcdba-director-fpa-and-grant-management-human-rights-watch-new-york</t>
+  </si>
+  <si>
     <t>Drupal Developer, Ongoing Site Maintenance (Contract, Remote)</t>
   </si>
   <si>
@@ -1000,6 +1279,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/12687369f84a4cb7b55de7793a580135-education-advocate-immigrant-students-rights-project-advocates-for-children-of-new-york-inc-new-york</t>
   </si>
   <si>
+    <t>Environmental Advocate</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ebb93f47b404c7f90df4bbcbb3db5fa-environmental-advocate-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Environmental Field Organizer</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 41000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3dbdcf718ff46e5bac3126ef413e720-environmental-field-organizer-green-corps-charleston</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c46a8bb79fc8439cb2a7d1a8dedf1014-environmental-field-organizer-green-corps-albuquerque</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab6f10aa3dcf4315957cabf456ed1bc6-environmental-field-organizer-green-corps-indianapolis</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95af34ff27bc4257b8402544dca632fe-environmental-field-organizer-green-corps-new-orleans</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f97c16444934a82882f23cf8e63c2ff-environmental-field-organizer-green-corps-miami</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50102ef814af43b6b30cc4607aaec41e-environmental-field-organizer-green-corps-boston</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/437fe1ea6dd94bed94ae30235e7bd067-environmental-field-organizer-green-corps-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a023893f293d492899a566c9cf3b32bc-environmental-field-organizer-green-corps-chicago</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/893074df75174b2aa00b0b2711212d64-environmental-field-organizer-green-corps-minneapolis</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bd0d8b2ad074024852b468bc0e7ac9a-environmental-field-organizer-green-corps-dallas</t>
+  </si>
+  <si>
+    <t>Eviction Defense (UD) Housing Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5d67cbe162649aa97481b2b97b158c5-eviction-defense-ud-housing-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>Laguna Beach, California</t>
   </si>
   <si>
@@ -1045,6 +1411,24 @@
     <t>https://www.idealist.org/en/job/c0bb3c557695437aa1d2edc60f9250ab-executive-director-for-the-master-of-professional-accountancy-program-university-of-california-san-diego-la-jolla</t>
   </si>
   <si>
+    <t>Executive Director, Kids Feeding Kids</t>
+  </si>
+  <si>
+    <t>Pete's Garden</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f75bf06b16444a8fb699b63c66e40dac-executive-director-kids-feeding-kids-petes-garden-kansas-city</t>
+  </si>
+  <si>
     <t>Executive Director, Midwest Chapter</t>
   </si>
   <si>
@@ -1075,6 +1459,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/4914c46e02f14526902d7c73d9e995e6-facilities-manager-triangle-land-conservancy-raleigh</t>
   </si>
   <si>
+    <t>Federal Environmental Campaigns Director</t>
+  </si>
+  <si>
+    <t>USD 43500.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a572c4db85f54d5099fffeff76d4949e-federal-environmental-campaigns-director-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Government Contract Manager</t>
+  </si>
+  <si>
+    <t>More Than Words</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b61543ab714d469a8e406f1ceeadd0ff-government-contract-manager-more-than-words-boston</t>
+  </si>
+  <si>
     <t>Grants and Partnerships Manager</t>
   </si>
   <si>
@@ -1105,6 +1516,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0a5fa78aeed045a2a7f861156e085dce-grants-manager-national-association-of-criminal-defense-lawyers-washington</t>
   </si>
   <si>
+    <t>HIGH SCHOOL COORDINATOR, COLLEGE &amp; CAREERS (EVANSTON)</t>
+  </si>
+  <si>
+    <t>MetroSquash</t>
+  </si>
+  <si>
+    <t>Evanston, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a7d45a2a9bf4f9fa544de7a197c946b-high-school-coordinator-college-careers-evanston-metrosquash-evanston</t>
+  </si>
+  <si>
     <t>Home Delivered Meals Driver - Full-time</t>
   </si>
   <si>
@@ -1132,9 +1561,6 @@
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/360dcc5cd97c456e8dbccd41f0a772c5-human-resources-office-coordinator-paintcare-american-coatings-association-washington</t>
   </si>
   <si>
@@ -1156,9 +1582,6 @@
     <t>AIDS Center of Queens County, Inc. - ACQC</t>
   </si>
   <si>
-    <t>Queens County, New York</t>
-  </si>
-  <si>
     <t>USD 51.00 - 51.00/hour</t>
   </si>
   <si>
@@ -1168,6 +1591,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/38f7124ff1e9410f8ee37cfff3b3da27-immigration-attorney-pt-aids-center-of-queens-county-inc-acqc-queens-county</t>
   </si>
   <si>
+    <t>IMMIGRATION LAW ATTORNEY CWJC (Worcester)</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccef51688be745edba86f70e9c789d97-immigration-law-attorney-cwjc-worcester-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
     <t>International Director 2027</t>
   </si>
   <si>
@@ -1189,9 +1630,6 @@
     <t>Toolworks</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 22.31 - 22.31/hour</t>
   </si>
   <si>
@@ -1213,6 +1651,39 @@
     <t>https://www.idealist.org/en/consultant-job/1afeb73d057541138a287dedffa6f866-junior-research-analyst-data-management-the-policy-and-research-group-new-orleans</t>
   </si>
   <si>
+    <t>Lead Janitor-II</t>
+  </si>
+  <si>
+    <t>USD 21.81 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86ac4326d1ec48169e5ac75df7065953-lead-janitor-ii-toolworks-san-francisco</t>
+  </si>
+  <si>
+    <t>Manager – Technology &amp; Data</t>
+  </si>
+  <si>
+    <t>Saturday Art Class</t>
+  </si>
+  <si>
+    <t>Mumbai, Maharastra, IN</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13e068e918ae4ad1bbab7af57fce55c4-manager-technology-data-saturday-art-class-mumbai</t>
+  </si>
+  <si>
+    <t>Manager, Strategic Alliances (Corporate Partnerships)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5bf3dd6bdfe49d5bb8ef0a2ded75ef3-manager-strategic-alliances-corporate-partnerships-first-book-washington</t>
+  </si>
+  <si>
     <t>Marketing &amp; Communications Manager</t>
   </si>
   <si>
@@ -1222,6 +1693,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4724cd509ebf4ac7a669969f181f7c7d-marketing-communications-manager-leadership-greater-washington-washington</t>
   </si>
   <si>
+    <t>Marketing &amp; Growth Manager</t>
+  </si>
+  <si>
+    <t>Challenge Success</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/948252efafb543a4b952b698075b5ae4-marketing-growth-manager-challenge-success-stanford</t>
+  </si>
+  <si>
     <t>Marketing and Content Manager</t>
   </si>
   <si>
@@ -1246,6 +1732,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/024c500481ea44f9bd08effd56c464fe-mass-care-organizer-mass-care-boston</t>
   </si>
   <si>
+    <t>MEL Director</t>
+  </si>
+  <si>
+    <t>Nuru International</t>
+  </si>
+  <si>
+    <t>USD 108000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2df480158374c3b9b406762e74f9d28-mel-director-nuru-international-washington</t>
+  </si>
+  <si>
     <t>Metascience Fellowship</t>
   </si>
   <si>
@@ -1261,6 +1762,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/5f7105113a604997a4f1a825105a461a-metascience-fellowship-federation-of-american-scientists-washington</t>
   </si>
   <si>
+    <t>Nonprofit Bookkeeper</t>
+  </si>
+  <si>
+    <t>Shorefront Legacy Center</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ad8af7084204873a29d2e286eb14a3c-nonprofit-bookkeeper-shorefront-legacy-center-evanston</t>
+  </si>
+  <si>
+    <t>Nonprofit Operations &amp; Communications Coordinator</t>
+  </si>
+  <si>
+    <t>SATB2 Gene Foundation</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2323ebc0429a45acbbef31bb0b1618b2-nonprofit-operations-communications-coordinator-satb2-gene-foundation-snellville</t>
+  </si>
+  <si>
+    <t>Now Recruiting PAID Mentors | MCIP Afterschool Mentoring Initiative (Washington, DC)</t>
+  </si>
+  <si>
+    <t>Multicultural Career Intern Program</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72c7311647e546828ce4c2f7062d79e6-now-recruiting-paid-mentors-mcip-afterschool-mentoring-initiative-washington-dc-multicultural-career-intern-program-washington</t>
+  </si>
+  <si>
     <t>Office and Facilities Manager</t>
   </si>
   <si>
@@ -1288,6 +1828,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/23cee5036ae7426fa5212af0a3fb8f2f-officer-business-partnerships-city-harvest-kings-county</t>
   </si>
   <si>
+    <t>Operations and Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/037dc17ee3674574aa56b210cf6b3a22-operations-and-administrative-coordinator-habitat-for-humanity-of-oregon-tualatin</t>
+  </si>
+  <si>
     <t>Operations Coordinator</t>
   </si>
   <si>
@@ -1318,6 +1864,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/ad27c925ccd8424d962e7a12641ec286-operations-specialist-sanar-institute-newark</t>
   </si>
   <si>
+    <t>Partnerships Account Manager</t>
+  </si>
+  <si>
+    <t>The LA Local</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79f3f0d8d5d34ebba5199e3d1a9c9b8f-partnerships-account-manager-the-la-local-los-angeles</t>
+  </si>
+  <si>
+    <t>Patron Services Assistant</t>
+  </si>
+  <si>
+    <t>RICHMOND SYMPHONY</t>
+  </si>
+  <si>
+    <t>USD 32000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9240fe4631fe4a0daff41b3b0038c0ca-patron-services-assistant-richmond-symphony-richmond</t>
+  </si>
+  <si>
     <t>President &amp; CEO</t>
   </si>
   <si>
@@ -1336,6 +1915,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/a6b83300d23c4db3a10b48c766302d0c-president-ceo-adagio-health-pittsburgh</t>
   </si>
   <si>
+    <t>Product Support Specialist</t>
+  </si>
+  <si>
+    <t>Illinois Legal Aid Online (ILAO)</t>
+  </si>
+  <si>
+    <t>Remote (Chicago, Illinois)</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1493ceb2f4624e5b9758de47829a72cd-product-support-specialist-illinois-legal-aid-online-ilao-chicago</t>
+  </si>
+  <si>
+    <t>Program Associate - Care Management</t>
+  </si>
+  <si>
+    <t>Safe &amp; Sound</t>
+  </si>
+  <si>
+    <t>USD 36.47/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29d4cccc2b114f19ad1b162621a96b9d-program-associate-care-management-safe-sound-san-francisco</t>
+  </si>
+  <si>
     <t>PT Legal Navigator</t>
   </si>
   <si>
@@ -1399,6 +2008,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/faa4583e8c45447c8b4f439540a4b2db-research-manager-united-way-of-northern-new-jersey-cedar-knolls</t>
   </si>
   <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 82500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a686cce9fb254090bf2362e673c505f4-senior-accountant-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
     <t>Senior Attorney- Equal Access and Housing</t>
   </si>
   <si>
@@ -1417,6 +2038,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/611a4727475f4619b05ff53cade42d4e-senior-attorney-equal-access-and-housing-disability-rights-california-sacramento</t>
   </si>
   <si>
+    <t>Senior Directing Attorney</t>
+  </si>
+  <si>
+    <t>USD 151500.00 - 179400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e8163542b7941a2b5c7de04d5e8b7df-senior-directing-attorney-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
+    <t>Senior Government Relations Specialist</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Massachusetts (ACLUM)</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b081adf03f4420ea1a4dc9c2cce7246-senior-government-relations-specialist-american-civil-liberties-union-of-massachusetts-aclum-boston</t>
+  </si>
+  <si>
     <t>Senior Grant Writer</t>
   </si>
   <si>
@@ -1429,6 +2071,30 @@
     <t>https://www.idealist.org/en/consultant-job/22b18aa754b34708b76c7b12ac3e227e-senior-grant-writer-elevate-washington</t>
   </si>
   <si>
+    <t>The Fortune Society</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/562fb95014354ffca53677c0fdd5e675-senior-grant-writer-the-fortune-society-queens-county</t>
+  </si>
+  <si>
+    <t>Senior Manager – Fundraising</t>
+  </si>
+  <si>
+    <t>Mumbai, Maharashtra, IN</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee962158105943bd9b94aa188a024214-senior-manager-fundraising-saturday-art-class-mumbai</t>
+  </si>
+  <si>
+    <t>Senior Manager – Partnerships &amp; Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e970b55bc564fb598539cb4b1b5fbf8-senior-manager-partnerships-operations-saturday-art-class-mumbai</t>
+  </si>
+  <si>
     <t>Senior Manager of Finance</t>
   </si>
   <si>
@@ -1465,6 +2131,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/97b3643dec4e4b549a6fbf3ff6151d7e-senior-manager-community-relations-spoonfuls-newton</t>
   </si>
   <si>
+    <t>Senior Manager, Education Program Operations</t>
+  </si>
+  <si>
+    <t>Lymphoma Research Foundation</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e68a54ee6efb411f92cc19e018091962-senior-manager-education-program-operations-lymphoma-research-foundation-new-york</t>
+  </si>
+  <si>
     <t>Senior Manager, Risk Behavior Prevention (CO Only)</t>
   </si>
   <si>
@@ -1483,6 +2161,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/d131c2b7199149a8bcd17b3c32e8fb8c-senior-manager-risk-behavior-prevention-co-only-action-for-healthy-kids-chicago</t>
   </si>
   <si>
+    <t>Senior Research Grants Manager</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/caa6e7afa0424b8baef63697c338b946-senior-research-grants-manager-lymphoma-research-foundation-new-york</t>
+  </si>
+  <si>
     <t>Senior Vice President, Partnership Fund for New York City</t>
   </si>
   <si>
@@ -1513,6 +2200,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/7924002f6dc34c65ad76eb8e983ab313-staff-attorney-shalom-task-force-inc-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney (Pro Bono - Appellate Practice &amp; Access to Justice)</t>
+  </si>
+  <si>
+    <t>Public Counsel</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 8400.01 - 124384.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa644b1169764b3c93a657a1f6ac4ab4-staff-attorney-pro-bono-appellate-practice-access-to-justice-public-counsel-los-angeles</t>
+  </si>
+  <si>
     <t>SUBDIRECTOR/A DE INSTITUTOS SUPERIORES</t>
   </si>
   <si>
@@ -1528,6 +2233,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/acfd94fe106142d3b559a8b46a06594f-subdirectora-de-institutos-superiores-cruz-roja-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Southeast Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cf6c340a2e04f01a08467ad571ff701-tutor-southeast-community-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Video Producer/Animator and Editor</t>
+  </si>
+  <si>
+    <t>amfAR</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5f7b10269d946bf9922404bb5659d8f-video-produceranimator-and-editor-amfar-new-york</t>
+  </si>
+  <si>
+    <t>Virginia Conservation Campaigner</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/376a156a1f9d4a1bb30f6d39fbc332bc-virginia-conservation-campaigner-environment-america-richmond</t>
+  </si>
+  <si>
+    <t>VISTA Program Manager</t>
+  </si>
+  <si>
+    <t>L.A. Works</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07475b35fabc4b25bdbb79dfc8d5a3cc-vista-program-manager-la-works-los-angeles</t>
+  </si>
+  <si>
     <t>Volunteer &amp; Community Engagement Associate</t>
   </si>
   <si>
@@ -1538,6 +2291,30 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/57b772ac3c81466b8307a3817313c365-volunteer-community-engagement-associate-jewish-family-service-of-metrowest-framingham</t>
+  </si>
+  <si>
+    <t>Volunteer Prison Ministry Assistant</t>
+  </si>
+  <si>
+    <t>Good News Jail and Prison Ministry Tanzania</t>
+  </si>
+  <si>
+    <t>MBEYA, Mbeya, TZ</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f1b3bf0d5314911a0a73f5b81cdd8df-volunteer-prison-ministry-assistant-good-news-jail-and-prison-ministry-tanzania-mbeya</t>
+  </si>
+  <si>
+    <t>Yale Peabody Museum Events Intern</t>
+  </si>
+  <si>
+    <t>Yale University</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/35a9c49b4149411194d05f38733c48b4-yale-peabody-museum-events-intern-yale-university-new-haven</t>
   </si>
   <si>
     <t>Youth Engagement Specialist</t>
@@ -2806,7 +3583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2902,7 +3679,7 @@
         <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E4" t="s">
         <v>202</v>
@@ -2945,16 +3722,16 @@
         <v>212</v>
       </c>
       <c r="C6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>214</v>
-      </c>
-      <c r="F6" t="s">
-        <v>209</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>215</v>
@@ -2985,137 +3762,137 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" t="s">
         <v>222</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
         <v>223</v>
       </c>
-      <c r="C8" t="s">
+      <c r="H8" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="D8" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" t="s">
-        <v>227</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="B9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" t="s">
-        <v>232</v>
-      </c>
-      <c r="F9" t="s">
-        <v>182</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" t="s">
         <v>234</v>
       </c>
-      <c r="B10" t="s">
+      <c r="H10" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="C10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" t="s">
-        <v>237</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
         <v>239</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F11" t="s">
         <v>240</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H11" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" t="s">
-        <v>242</v>
-      </c>
-      <c r="F11" t="s">
-        <v>243</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" t="s">
         <v>245</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>246</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>247</v>
       </c>
-      <c r="D12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E12" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
         <v>250</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>251</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" t="s">
         <v>252</v>
       </c>
-      <c r="D13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>253</v>
-      </c>
-      <c r="F13" t="s">
-        <v>182</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>254</v>
@@ -3138,665 +3915,662 @@
         <v>258</v>
       </c>
       <c r="F14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" t="s">
         <v>261</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>262</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" t="s">
         <v>263</v>
       </c>
-      <c r="D15" t="s">
-        <v>188</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>264</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B16" t="s">
         <v>267</v>
       </c>
       <c r="C16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" t="s">
         <v>268</v>
       </c>
-      <c r="D16" t="s">
-        <v>188</v>
-      </c>
       <c r="E16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" t="s">
         <v>269</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s">
         <v>272</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>273</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
         <v>274</v>
       </c>
-      <c r="D17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>275</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B18" t="s">
         <v>278</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>279</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" t="s">
         <v>280</v>
       </c>
-      <c r="D18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="F18" t="s">
-        <v>282</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" t="s">
         <v>284</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
         <v>285</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>286</v>
       </c>
-      <c r="D19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="H19" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="F19" t="s">
-        <v>288</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C20" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
         <v>188</v>
       </c>
       <c r="E20" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F20" t="s">
-        <v>288</v>
+        <v>182</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B21" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D21" t="s">
         <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F21" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C22" t="s">
-        <v>207</v>
+        <v>300</v>
       </c>
       <c r="D22" t="s">
         <v>188</v>
       </c>
       <c r="E22" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C23" t="s">
-        <v>213</v>
+        <v>306</v>
       </c>
       <c r="D23" t="s">
         <v>188</v>
       </c>
       <c r="E23" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F23" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C24" t="s">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="D24" t="s">
         <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="F24" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B25" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C25" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="D25" t="s">
         <v>188</v>
       </c>
       <c r="E25" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F25" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D26" t="s">
         <v>188</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F26" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B27" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>329</v>
       </c>
       <c r="D27" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>330</v>
       </c>
       <c r="F27" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B28" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C28" t="s">
-        <v>213</v>
+        <v>335</v>
       </c>
       <c r="D28" t="s">
         <v>188</v>
       </c>
       <c r="E28" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="F28" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D29" t="s">
         <v>188</v>
       </c>
       <c r="E29" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F29" t="s">
-        <v>330</v>
-      </c>
-      <c r="G29" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C30" t="s">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
         <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F30" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B31" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C31" t="s">
-        <v>341</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
         <v>188</v>
       </c>
       <c r="E31" t="s">
-        <v>182</v>
+        <v>347</v>
       </c>
       <c r="F31" t="s">
         <v>182</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="D32" t="s">
         <v>188</v>
       </c>
       <c r="E32" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F32" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B33" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C33" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D33" t="s">
         <v>188</v>
       </c>
       <c r="E33" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F33" t="s">
-        <v>351</v>
+        <v>182</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="E34" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
-        <v>248</v>
+        <v>362</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C35" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D35" t="s">
         <v>188</v>
       </c>
       <c r="E35" t="s">
-        <v>202</v>
+        <v>366</v>
       </c>
       <c r="F35" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C36" t="s">
-        <v>365</v>
+        <v>201</v>
       </c>
       <c r="D36" t="s">
         <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F36" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="D37" t="s">
         <v>188</v>
       </c>
       <c r="E37" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F37" t="s">
-        <v>372</v>
+        <v>182</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="C38" t="s">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="D38" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E38" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="F38" t="s">
-        <v>376</v>
+        <v>203</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>201</v>
       </c>
       <c r="D39" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E39" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F39" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="D40" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="E40" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F40" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C41" t="s">
-        <v>391</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
         <v>188</v>
       </c>
       <c r="E41" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F41" t="s">
         <v>182</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
+        <v>201</v>
+      </c>
+      <c r="D42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" t="s">
+        <v>383</v>
+      </c>
+      <c r="F42" t="s">
+        <v>384</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="D42" t="s">
-        <v>188</v>
-      </c>
-      <c r="E42" t="s">
-        <v>397</v>
-      </c>
-      <c r="F42" t="s">
-        <v>182</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C43" t="s">
         <v>187</v>
@@ -3805,10 +4579,10 @@
         <v>188</v>
       </c>
       <c r="E43" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="F43" t="s">
-        <v>299</v>
+        <v>400</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>401</v>
@@ -3822,502 +4596,1977 @@
         <v>403</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>404</v>
       </c>
       <c r="D44" t="s">
         <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F44" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" t="s">
-        <v>365</v>
+        <v>227</v>
       </c>
       <c r="D45" t="s">
         <v>188</v>
       </c>
       <c r="E45" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F45" t="s">
-        <v>209</v>
+        <v>410</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="D46" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="E46" t="s">
-        <v>412</v>
+        <v>182</v>
       </c>
       <c r="F46" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
       <c r="C47" t="s">
-        <v>360</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
         <v>188</v>
       </c>
       <c r="E47" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F47" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
-        <v>420</v>
+        <v>283</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>422</v>
       </c>
       <c r="D48" t="s">
         <v>188</v>
       </c>
       <c r="E48" t="s">
-        <v>421</v>
+        <v>296</v>
       </c>
       <c r="F48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C49" t="s">
-        <v>207</v>
+        <v>427</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="E49" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F49" t="s">
-        <v>427</v>
+        <v>286</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s">
+        <v>426</v>
+      </c>
+      <c r="C50" t="s">
         <v>430</v>
       </c>
-      <c r="C50" t="s">
-        <v>293</v>
-      </c>
       <c r="D50" t="s">
         <v>188</v>
       </c>
       <c r="E50" t="s">
+        <v>428</v>
+      </c>
+      <c r="F50" t="s">
+        <v>286</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="F50" t="s">
-        <v>432</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C51" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D51" t="s">
         <v>188</v>
       </c>
       <c r="E51" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F51" t="s">
-        <v>438</v>
+        <v>286</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s">
-        <v>379</v>
+        <v>426</v>
       </c>
       <c r="C52" t="s">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="D52" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E52" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="F52" t="s">
-        <v>382</v>
+        <v>286</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C53" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D53" t="s">
         <v>188</v>
       </c>
       <c r="E53" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="F53" t="s">
-        <v>447</v>
+        <v>286</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="C54" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="D54" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E54" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="F54" t="s">
-        <v>453</v>
+        <v>286</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="B55" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="C55" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D55" t="s">
         <v>188</v>
       </c>
       <c r="E55" t="s">
-        <v>458</v>
+        <v>428</v>
       </c>
       <c r="F55" t="s">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="C56" t="s">
-        <v>463</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
         <v>188</v>
       </c>
       <c r="E56" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="F56" t="s">
-        <v>465</v>
+        <v>286</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>466</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>442</v>
       </c>
       <c r="D57" t="s">
         <v>188</v>
       </c>
       <c r="E57" t="s">
-        <v>469</v>
+        <v>428</v>
       </c>
       <c r="F57" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>471</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s">
-        <v>472</v>
+        <v>426</v>
       </c>
       <c r="C58" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="D58" t="s">
         <v>188</v>
       </c>
       <c r="E58" t="s">
-        <v>474</v>
+        <v>428</v>
       </c>
       <c r="F58" t="s">
-        <v>475</v>
+        <v>286</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="C59" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="D59" t="s">
         <v>188</v>
       </c>
       <c r="E59" t="s">
-        <v>480</v>
+        <v>182</v>
       </c>
       <c r="F59" t="s">
-        <v>481</v>
+        <v>182</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>483</v>
+        <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>484</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="D60" t="s">
         <v>188</v>
       </c>
       <c r="E60" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="F60" t="s">
-        <v>487</v>
+        <v>452</v>
+      </c>
+      <c r="G60" t="s">
+        <v>453</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>488</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="C61" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="D61" t="s">
         <v>188</v>
       </c>
       <c r="E61" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="F61" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>494</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s">
-        <v>302</v>
+        <v>462</v>
       </c>
       <c r="C62" t="s">
-        <v>213</v>
+        <v>463</v>
       </c>
       <c r="D62" t="s">
         <v>188</v>
       </c>
       <c r="E62" t="s">
-        <v>496</v>
+        <v>182</v>
       </c>
       <c r="F62" t="s">
-        <v>497</v>
+        <v>182</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>499</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="C63" t="s">
-        <v>501</v>
+        <v>467</v>
       </c>
       <c r="D63" t="s">
         <v>188</v>
       </c>
       <c r="E63" t="s">
-        <v>502</v>
+        <v>468</v>
       </c>
       <c r="F63" t="s">
-        <v>317</v>
+        <v>469</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s">
-        <v>450</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>451</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
         <v>188</v>
       </c>
       <c r="E64" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="F64" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>475</v>
+      </c>
+      <c r="B65" t="s">
+        <v>476</v>
+      </c>
+      <c r="C65" t="s">
+        <v>477</v>
+      </c>
+      <c r="D65" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" t="s">
+        <v>478</v>
+      </c>
+      <c r="F65" t="s">
+        <v>479</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>481</v>
+      </c>
+      <c r="B66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C66" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" t="s">
+        <v>188</v>
+      </c>
+      <c r="E66" t="s">
+        <v>482</v>
+      </c>
+      <c r="F66" t="s">
+        <v>483</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>485</v>
+      </c>
+      <c r="B67" t="s">
+        <v>486</v>
+      </c>
+      <c r="C67" t="s">
+        <v>422</v>
+      </c>
+      <c r="D67" t="s">
+        <v>188</v>
+      </c>
+      <c r="E67" t="s">
+        <v>487</v>
+      </c>
+      <c r="F67" t="s">
+        <v>488</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>490</v>
+      </c>
+      <c r="B68" t="s">
+        <v>491</v>
+      </c>
+      <c r="C68" t="s">
+        <v>492</v>
+      </c>
+      <c r="D68" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" t="s">
+        <v>493</v>
+      </c>
+      <c r="F68" t="s">
+        <v>280</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>495</v>
+      </c>
+      <c r="B69" t="s">
+        <v>496</v>
+      </c>
+      <c r="C69" t="s">
+        <v>497</v>
+      </c>
+      <c r="D69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" t="s">
+        <v>208</v>
+      </c>
+      <c r="F69" t="s">
+        <v>498</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>500</v>
+      </c>
+      <c r="B70" t="s">
+        <v>501</v>
+      </c>
+      <c r="C70" t="s">
+        <v>502</v>
+      </c>
+      <c r="D70" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" t="s">
+        <v>504</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>506</v>
+      </c>
+      <c r="B71" t="s">
+        <v>507</v>
+      </c>
+      <c r="C71" t="s">
         <v>508</v>
       </c>
-      <c r="B65" t="s">
+      <c r="D71" t="s">
+        <v>188</v>
+      </c>
+      <c r="E71" t="s">
         <v>509</v>
       </c>
-      <c r="C65" t="s">
-        <v>213</v>
-      </c>
-      <c r="D65" t="s">
-        <v>188</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F71" t="s">
         <v>510</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H71" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>512</v>
+      </c>
+      <c r="B72" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" t="s">
+        <v>188</v>
+      </c>
+      <c r="E72" t="s">
+        <v>514</v>
+      </c>
+      <c r="F72" t="s">
+        <v>286</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>516</v>
+      </c>
+      <c r="B73" t="s">
+        <v>517</v>
+      </c>
+      <c r="C73" t="s">
+        <v>497</v>
+      </c>
+      <c r="D73" t="s">
+        <v>188</v>
+      </c>
+      <c r="E73" t="s">
+        <v>399</v>
+      </c>
+      <c r="F73" t="s">
+        <v>518</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>520</v>
+      </c>
+      <c r="B74" t="s">
+        <v>521</v>
+      </c>
+      <c r="C74" t="s">
+        <v>262</v>
+      </c>
+      <c r="D74" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" t="s">
+        <v>522</v>
+      </c>
+      <c r="F74" t="s">
+        <v>523</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>525</v>
+      </c>
+      <c r="B75" t="s">
+        <v>526</v>
+      </c>
+      <c r="C75" t="s">
+        <v>527</v>
+      </c>
+      <c r="D75" t="s">
+        <v>188</v>
+      </c>
+      <c r="E75" t="s">
+        <v>528</v>
+      </c>
+      <c r="F75" t="s">
+        <v>529</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>531</v>
+      </c>
+      <c r="B76" t="s">
+        <v>532</v>
+      </c>
+      <c r="C76" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" t="s">
+        <v>268</v>
+      </c>
+      <c r="E76" t="s">
+        <v>533</v>
+      </c>
+      <c r="F76" t="s">
+        <v>534</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>536</v>
+      </c>
+      <c r="B77" t="s">
+        <v>537</v>
+      </c>
+      <c r="C77" t="s">
+        <v>448</v>
+      </c>
+      <c r="D77" t="s">
+        <v>188</v>
+      </c>
+      <c r="E77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77" t="s">
         <v>182</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>511</v>
+      <c r="H77" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>540</v>
+      </c>
+      <c r="B78" t="s">
+        <v>541</v>
+      </c>
+      <c r="C78" t="s">
+        <v>542</v>
+      </c>
+      <c r="D78" t="s">
+        <v>188</v>
+      </c>
+      <c r="E78" t="s">
+        <v>543</v>
+      </c>
+      <c r="F78" t="s">
+        <v>182</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>545</v>
+      </c>
+      <c r="B79" t="s">
+        <v>537</v>
+      </c>
+      <c r="C79" t="s">
+        <v>448</v>
+      </c>
+      <c r="D79" t="s">
+        <v>188</v>
+      </c>
+      <c r="E79" t="s">
+        <v>546</v>
+      </c>
+      <c r="F79" t="s">
+        <v>182</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>548</v>
+      </c>
+      <c r="B80" t="s">
+        <v>549</v>
+      </c>
+      <c r="C80" t="s">
+        <v>550</v>
+      </c>
+      <c r="D80" t="s">
+        <v>188</v>
+      </c>
+      <c r="E80" t="s">
+        <v>182</v>
+      </c>
+      <c r="F80" t="s">
+        <v>551</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>553</v>
+      </c>
+      <c r="B81" t="s">
+        <v>341</v>
+      </c>
+      <c r="C81" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" t="s">
+        <v>554</v>
+      </c>
+      <c r="F81" t="s">
+        <v>343</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>556</v>
+      </c>
+      <c r="B82" t="s">
+        <v>557</v>
+      </c>
+      <c r="C82" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" t="s">
+        <v>188</v>
+      </c>
+      <c r="E82" t="s">
+        <v>458</v>
+      </c>
+      <c r="F82" t="s">
+        <v>384</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>559</v>
+      </c>
+      <c r="B83" t="s">
+        <v>560</v>
+      </c>
+      <c r="C83" t="s">
+        <v>201</v>
+      </c>
+      <c r="D83" t="s">
+        <v>188</v>
+      </c>
+      <c r="E83" t="s">
+        <v>561</v>
+      </c>
+      <c r="F83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>564</v>
+      </c>
+      <c r="B84" t="s">
+        <v>565</v>
+      </c>
+      <c r="C84" t="s">
+        <v>227</v>
+      </c>
+      <c r="D84" t="s">
+        <v>188</v>
+      </c>
+      <c r="E84" t="s">
+        <v>566</v>
+      </c>
+      <c r="F84" t="s">
+        <v>280</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>568</v>
+      </c>
+      <c r="B85" t="s">
+        <v>569</v>
+      </c>
+      <c r="C85" t="s">
+        <v>508</v>
+      </c>
+      <c r="D85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85" t="s">
+        <v>570</v>
+      </c>
+      <c r="F85" t="s">
+        <v>214</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>572</v>
+      </c>
+      <c r="B86" t="s">
+        <v>573</v>
+      </c>
+      <c r="C86" t="s">
+        <v>201</v>
+      </c>
+      <c r="D86" t="s">
+        <v>188</v>
+      </c>
+      <c r="E86" t="s">
+        <v>574</v>
+      </c>
+      <c r="F86" t="s">
+        <v>575</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>577</v>
+      </c>
+      <c r="B87" t="s">
+        <v>578</v>
+      </c>
+      <c r="C87" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" t="s">
+        <v>268</v>
+      </c>
+      <c r="E87" t="s">
+        <v>579</v>
+      </c>
+      <c r="F87" t="s">
+        <v>580</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>582</v>
+      </c>
+      <c r="B88" t="s">
+        <v>583</v>
+      </c>
+      <c r="C88" t="s">
+        <v>502</v>
+      </c>
+      <c r="D88" t="s">
+        <v>195</v>
+      </c>
+      <c r="E88" t="s">
+        <v>584</v>
+      </c>
+      <c r="F88" t="s">
+        <v>585</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>587</v>
+      </c>
+      <c r="B89" t="s">
+        <v>588</v>
+      </c>
+      <c r="C89" t="s">
+        <v>201</v>
+      </c>
+      <c r="D89" t="s">
+        <v>195</v>
+      </c>
+      <c r="E89" t="s">
+        <v>589</v>
+      </c>
+      <c r="F89" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>591</v>
+      </c>
+      <c r="B90" t="s">
+        <v>592</v>
+      </c>
+      <c r="C90" t="s">
+        <v>187</v>
+      </c>
+      <c r="D90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E90" t="s">
+        <v>593</v>
+      </c>
+      <c r="F90" t="s">
+        <v>331</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>595</v>
+      </c>
+      <c r="B91" t="s">
+        <v>517</v>
+      </c>
+      <c r="C91" t="s">
+        <v>497</v>
+      </c>
+      <c r="D91" t="s">
+        <v>188</v>
+      </c>
+      <c r="E91" t="s">
+        <v>596</v>
+      </c>
+      <c r="F91" t="s">
+        <v>597</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>599</v>
+      </c>
+      <c r="B92" t="s">
+        <v>600</v>
+      </c>
+      <c r="C92" t="s">
+        <v>194</v>
+      </c>
+      <c r="D92" t="s">
+        <v>188</v>
+      </c>
+      <c r="E92" t="s">
+        <v>601</v>
+      </c>
+      <c r="F92" t="s">
+        <v>602</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>604</v>
+      </c>
+      <c r="B93" t="s">
+        <v>350</v>
+      </c>
+      <c r="C93" t="s">
+        <v>351</v>
+      </c>
+      <c r="D93" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93" t="s">
+        <v>352</v>
+      </c>
+      <c r="F93" t="s">
+        <v>353</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>606</v>
+      </c>
+      <c r="B94" t="s">
+        <v>607</v>
+      </c>
+      <c r="C94" t="s">
+        <v>201</v>
+      </c>
+      <c r="D94" t="s">
+        <v>245</v>
+      </c>
+      <c r="E94" t="s">
+        <v>608</v>
+      </c>
+      <c r="F94" t="s">
+        <v>609</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>611</v>
+      </c>
+      <c r="B95" t="s">
+        <v>612</v>
+      </c>
+      <c r="C95" t="s">
+        <v>357</v>
+      </c>
+      <c r="D95" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" t="s">
+        <v>613</v>
+      </c>
+      <c r="F95" t="s">
+        <v>614</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>616</v>
+      </c>
+      <c r="B96" t="s">
+        <v>617</v>
+      </c>
+      <c r="C96" t="s">
+        <v>618</v>
+      </c>
+      <c r="D96" t="s">
+        <v>188</v>
+      </c>
+      <c r="E96" t="s">
+        <v>619</v>
+      </c>
+      <c r="F96" t="s">
+        <v>620</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>622</v>
+      </c>
+      <c r="B97" t="s">
+        <v>623</v>
+      </c>
+      <c r="C97" t="s">
+        <v>290</v>
+      </c>
+      <c r="D97" t="s">
+        <v>188</v>
+      </c>
+      <c r="E97" t="s">
+        <v>624</v>
+      </c>
+      <c r="F97" t="s">
+        <v>625</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>627</v>
+      </c>
+      <c r="B98" t="s">
+        <v>628</v>
+      </c>
+      <c r="C98" t="s">
+        <v>629</v>
+      </c>
+      <c r="D98" t="s">
+        <v>188</v>
+      </c>
+      <c r="E98" t="s">
+        <v>630</v>
+      </c>
+      <c r="F98" t="s">
+        <v>631</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>633</v>
+      </c>
+      <c r="B99" t="s">
+        <v>634</v>
+      </c>
+      <c r="C99" t="s">
+        <v>635</v>
+      </c>
+      <c r="D99" t="s">
+        <v>188</v>
+      </c>
+      <c r="E99" t="s">
+        <v>636</v>
+      </c>
+      <c r="F99" t="s">
+        <v>182</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>638</v>
+      </c>
+      <c r="B100" t="s">
+        <v>639</v>
+      </c>
+      <c r="C100" t="s">
+        <v>448</v>
+      </c>
+      <c r="D100" t="s">
+        <v>188</v>
+      </c>
+      <c r="E100" t="s">
+        <v>640</v>
+      </c>
+      <c r="F100" t="s">
+        <v>641</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>643</v>
+      </c>
+      <c r="B101" t="s">
+        <v>521</v>
+      </c>
+      <c r="C101" t="s">
+        <v>262</v>
+      </c>
+      <c r="D101" t="s">
+        <v>195</v>
+      </c>
+      <c r="E101" t="s">
+        <v>644</v>
+      </c>
+      <c r="F101" t="s">
+        <v>523</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>646</v>
+      </c>
+      <c r="B102" t="s">
+        <v>647</v>
+      </c>
+      <c r="C102" t="s">
+        <v>648</v>
+      </c>
+      <c r="D102" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" t="s">
+        <v>649</v>
+      </c>
+      <c r="F102" t="s">
+        <v>650</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>652</v>
+      </c>
+      <c r="B103" t="s">
+        <v>653</v>
+      </c>
+      <c r="C103" t="s">
+        <v>654</v>
+      </c>
+      <c r="D103" t="s">
+        <v>195</v>
+      </c>
+      <c r="E103" t="s">
+        <v>655</v>
+      </c>
+      <c r="F103" t="s">
+        <v>656</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>658</v>
+      </c>
+      <c r="B104" t="s">
+        <v>659</v>
+      </c>
+      <c r="C104" t="s">
+        <v>660</v>
+      </c>
+      <c r="D104" t="s">
+        <v>188</v>
+      </c>
+      <c r="E104" t="s">
+        <v>661</v>
+      </c>
+      <c r="F104" t="s">
+        <v>662</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>664</v>
+      </c>
+      <c r="B105" t="s">
+        <v>231</v>
+      </c>
+      <c r="C105" t="s">
+        <v>665</v>
+      </c>
+      <c r="D105" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" t="s">
+        <v>666</v>
+      </c>
+      <c r="F105" t="s">
+        <v>234</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>668</v>
+      </c>
+      <c r="B106" t="s">
+        <v>669</v>
+      </c>
+      <c r="C106" t="s">
+        <v>670</v>
+      </c>
+      <c r="D106" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" t="s">
+        <v>671</v>
+      </c>
+      <c r="F106" t="s">
+        <v>672</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>674</v>
+      </c>
+      <c r="B107" t="s">
+        <v>231</v>
+      </c>
+      <c r="C107" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" t="s">
+        <v>188</v>
+      </c>
+      <c r="E107" t="s">
+        <v>675</v>
+      </c>
+      <c r="F107" t="s">
+        <v>234</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>677</v>
+      </c>
+      <c r="B108" t="s">
+        <v>678</v>
+      </c>
+      <c r="C108" t="s">
+        <v>422</v>
+      </c>
+      <c r="D108" t="s">
+        <v>188</v>
+      </c>
+      <c r="E108" t="s">
+        <v>679</v>
+      </c>
+      <c r="F108" t="s">
+        <v>410</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>681</v>
+      </c>
+      <c r="B109" t="s">
+        <v>682</v>
+      </c>
+      <c r="C109" t="s">
+        <v>201</v>
+      </c>
+      <c r="D109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" t="s">
+        <v>683</v>
+      </c>
+      <c r="F109" t="s">
+        <v>182</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>681</v>
+      </c>
+      <c r="B110" t="s">
+        <v>685</v>
+      </c>
+      <c r="C110" t="s">
+        <v>262</v>
+      </c>
+      <c r="D110" t="s">
+        <v>188</v>
+      </c>
+      <c r="E110" t="s">
+        <v>472</v>
+      </c>
+      <c r="F110" t="s">
+        <v>686</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>688</v>
+      </c>
+      <c r="B111" t="s">
+        <v>549</v>
+      </c>
+      <c r="C111" t="s">
+        <v>689</v>
+      </c>
+      <c r="D111" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" t="s">
+        <v>182</v>
+      </c>
+      <c r="F111" t="s">
+        <v>551</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>691</v>
+      </c>
+      <c r="B112" t="s">
+        <v>549</v>
+      </c>
+      <c r="C112" t="s">
+        <v>689</v>
+      </c>
+      <c r="D112" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" t="s">
+        <v>182</v>
+      </c>
+      <c r="F112" t="s">
+        <v>551</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>693</v>
+      </c>
+      <c r="B113" t="s">
+        <v>694</v>
+      </c>
+      <c r="C113" t="s">
+        <v>695</v>
+      </c>
+      <c r="D113" t="s">
+        <v>188</v>
+      </c>
+      <c r="E113" t="s">
+        <v>696</v>
+      </c>
+      <c r="F113" t="s">
+        <v>697</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>699</v>
+      </c>
+      <c r="B114" t="s">
+        <v>700</v>
+      </c>
+      <c r="C114" t="s">
+        <v>701</v>
+      </c>
+      <c r="D114" t="s">
+        <v>188</v>
+      </c>
+      <c r="E114" t="s">
+        <v>702</v>
+      </c>
+      <c r="F114" t="s">
+        <v>703</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>705</v>
+      </c>
+      <c r="B115" t="s">
+        <v>706</v>
+      </c>
+      <c r="C115" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" t="s">
+        <v>188</v>
+      </c>
+      <c r="E115" t="s">
+        <v>458</v>
+      </c>
+      <c r="F115" t="s">
+        <v>707</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>709</v>
+      </c>
+      <c r="B116" t="s">
+        <v>710</v>
+      </c>
+      <c r="C116" t="s">
+        <v>711</v>
+      </c>
+      <c r="D116" t="s">
+        <v>188</v>
+      </c>
+      <c r="E116" t="s">
+        <v>712</v>
+      </c>
+      <c r="F116" t="s">
+        <v>713</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>715</v>
+      </c>
+      <c r="B117" t="s">
+        <v>706</v>
+      </c>
+      <c r="C117" t="s">
+        <v>227</v>
+      </c>
+      <c r="D117" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" t="s">
+        <v>716</v>
+      </c>
+      <c r="F117" t="s">
+        <v>707</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>718</v>
+      </c>
+      <c r="B118" t="s">
+        <v>719</v>
+      </c>
+      <c r="C118" t="s">
+        <v>720</v>
+      </c>
+      <c r="D118" t="s">
+        <v>188</v>
+      </c>
+      <c r="E118" t="s">
+        <v>721</v>
+      </c>
+      <c r="F118" t="s">
+        <v>722</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>724</v>
+      </c>
+      <c r="B119" t="s">
+        <v>387</v>
+      </c>
+      <c r="C119" t="s">
+        <v>227</v>
+      </c>
+      <c r="D119" t="s">
+        <v>188</v>
+      </c>
+      <c r="E119" t="s">
+        <v>725</v>
+      </c>
+      <c r="F119" t="s">
+        <v>726</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>728</v>
+      </c>
+      <c r="B120" t="s">
+        <v>729</v>
+      </c>
+      <c r="C120" t="s">
+        <v>730</v>
+      </c>
+      <c r="D120" t="s">
+        <v>188</v>
+      </c>
+      <c r="E120" t="s">
+        <v>731</v>
+      </c>
+      <c r="F120" t="s">
+        <v>732</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>734</v>
+      </c>
+      <c r="B121" t="s">
+        <v>735</v>
+      </c>
+      <c r="C121" t="s">
+        <v>736</v>
+      </c>
+      <c r="D121" t="s">
+        <v>188</v>
+      </c>
+      <c r="E121" t="s">
+        <v>737</v>
+      </c>
+      <c r="F121" t="s">
+        <v>331</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>739</v>
+      </c>
+      <c r="B122" t="s">
+        <v>740</v>
+      </c>
+      <c r="C122" t="s">
+        <v>618</v>
+      </c>
+      <c r="D122" t="s">
+        <v>245</v>
+      </c>
+      <c r="E122" t="s">
+        <v>741</v>
+      </c>
+      <c r="F122" t="s">
+        <v>742</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>744</v>
+      </c>
+      <c r="B123" t="s">
+        <v>745</v>
+      </c>
+      <c r="C123" t="s">
+        <v>720</v>
+      </c>
+      <c r="D123" t="s">
+        <v>188</v>
+      </c>
+      <c r="E123" t="s">
+        <v>312</v>
+      </c>
+      <c r="F123" t="s">
+        <v>746</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>748</v>
+      </c>
+      <c r="B124" t="s">
+        <v>283</v>
+      </c>
+      <c r="C124" t="s">
+        <v>290</v>
+      </c>
+      <c r="D124" t="s">
+        <v>188</v>
+      </c>
+      <c r="E124" t="s">
+        <v>285</v>
+      </c>
+      <c r="F124" t="s">
+        <v>286</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>750</v>
+      </c>
+      <c r="B125" t="s">
+        <v>751</v>
+      </c>
+      <c r="C125" t="s">
+        <v>618</v>
+      </c>
+      <c r="D125" t="s">
+        <v>188</v>
+      </c>
+      <c r="E125" t="s">
+        <v>752</v>
+      </c>
+      <c r="F125" t="s">
+        <v>753</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>755</v>
+      </c>
+      <c r="B126" t="s">
+        <v>653</v>
+      </c>
+      <c r="C126" t="s">
+        <v>654</v>
+      </c>
+      <c r="D126" t="s">
+        <v>188</v>
+      </c>
+      <c r="E126" t="s">
+        <v>756</v>
+      </c>
+      <c r="F126" t="s">
+        <v>757</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>759</v>
+      </c>
+      <c r="B127" t="s">
+        <v>760</v>
+      </c>
+      <c r="C127" t="s">
+        <v>761</v>
+      </c>
+      <c r="D127" t="s">
+        <v>195</v>
+      </c>
+      <c r="E127" t="s">
+        <v>182</v>
+      </c>
+      <c r="F127" t="s">
+        <v>534</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>763</v>
+      </c>
+      <c r="B128" t="s">
+        <v>764</v>
+      </c>
+      <c r="C128" t="s">
+        <v>765</v>
+      </c>
+      <c r="D128" t="s">
+        <v>188</v>
+      </c>
+      <c r="E128" t="s">
+        <v>182</v>
+      </c>
+      <c r="F128" t="s">
+        <v>182</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>767</v>
+      </c>
+      <c r="B129" t="s">
+        <v>768</v>
+      </c>
+      <c r="C129" t="s">
+        <v>227</v>
+      </c>
+      <c r="D129" t="s">
+        <v>188</v>
+      </c>
+      <c r="E129" t="s">
+        <v>769</v>
+      </c>
+      <c r="F129" t="s">
+        <v>182</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -4387,6 +6636,70 @@
     <hyperlink ref="H63" r:id="rId62"/>
     <hyperlink ref="H64" r:id="rId63"/>
     <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
